--- a/branches/fix/muv-koerperlaenge-slicing/StructureDefinition-mii-pr-icu-vent-spontanes-plus-mechanisches-atemzugvolumen.xlsx
+++ b/branches/fix/muv-koerperlaenge-slicing/StructureDefinition-mii-pr-icu-vent-spontanes-plus-mechanisches-atemzugvolumen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T12:43:06+00:00</t>
+    <t>2026-09-29T13:08:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
